--- a/filter_instock.xlsx
+++ b/filter_instock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,6 +468,42 @@
         <is>
           <t>입고수량</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1785129649210</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock.xlsx
+++ b/filter_instock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,36 @@
       </c>
       <c r="H2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1785130401961</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock.xlsx
+++ b/filter_instock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,9 +531,41 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
       <c r="H3" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1785130438956</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock.xlsx
+++ b/filter_instock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,9 +563,41 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
       <c r="H4" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1785130478985</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock.xlsx
+++ b/filter_instock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,9 +595,47 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1785130521792</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock.xlsx
+++ b/filter_instock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,6 +636,36 @@
       </c>
       <c r="H6" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1785130891158</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock.xlsx
+++ b/filter_instock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,9 +663,47 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
       <c r="H7" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1785138779160</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PALL</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>70</v>
+      </c>
+      <c r="H8" t="n">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/filter_instock.xlsx
+++ b/filter_instock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -706,6 +706,42 @@
         <v>120</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1785138855575</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>70</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
